--- a/test_data/Data_Schools.xlsx
+++ b/test_data/Data_Schools.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kadellabs365-my.sharepoint.com/personal/tanisha_maratha_kadellabs_com/Documents/Desktop/CISCE/CISCE_Preliminary_Form_Automation_Main/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="920" documentId="8_{6340B17D-EE6B-4357-A810-F66C6FD39EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1D8EB42-94B6-43CD-BE2E-533503522DE7}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{00F80499-79F4-4643-BF32-36BE85123AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AF7B23B-FB31-4E49-AFAB-FEF864D19038}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="6" xr2:uid="{F1CF226F-ABD0-45BD-89FA-6994D6DA7451}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{F1CF226F-ABD0-45BD-89FA-6994D6DA7451}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="10" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="338">
   <si>
     <t>school_id</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>password</t>
-  </si>
-  <si>
-    <t>CACUSG</t>
   </si>
   <si>
     <t>school_name</t>
@@ -642,9 +639,6 @@
     <t>Test comments</t>
   </si>
   <si>
-    <t>Provisional Affiliation up to Class X</t>
-  </si>
-  <si>
     <t>Demo school upload</t>
   </si>
   <si>
@@ -684,9 +678,6 @@
     <t>Ryan International School</t>
   </si>
   <si>
-    <t>Sneha Soni</t>
-  </si>
-  <si>
     <t>Teachers Colony Sector 6</t>
   </si>
   <si>
@@ -747,34 +738,7 @@
     <t>Sonali Ved</t>
   </si>
   <si>
-    <t>Kartik Mahajan</t>
-  </si>
-  <si>
-    <t>NOC-AB11</t>
-  </si>
-  <si>
-    <t>rahul.7102323017@yopmail.com</t>
-  </si>
-  <si>
-    <t>neha.8189090889@yopmail.com</t>
-  </si>
-  <si>
-    <t>priya.9940409940@yopmail.com</t>
-  </si>
-  <si>
-    <t>raj.8930308930@yopmail.com</t>
-  </si>
-  <si>
-    <t>riya.9339337336@yopmail.com</t>
-  </si>
-  <si>
-    <t>kartik.9109883327@yopmail.com</t>
-  </si>
-  <si>
     <t>sonali.8398291920@yopmail.com</t>
-  </si>
-  <si>
-    <t>sneha.9020405020@yopmail.com</t>
   </si>
   <si>
     <t>Raj Sharma</t>
@@ -802,12 +766,6 @@
     <t>Quest Academy</t>
   </si>
   <si>
-    <t>Greenfield School</t>
-  </si>
-  <si>
-    <t>Loudoun School</t>
-  </si>
-  <si>
     <t>Powhatan School</t>
   </si>
   <si>
@@ -841,46 +799,256 @@
     <t>www.powhatanschoolday.com</t>
   </si>
   <si>
-    <t>NOC-AB12</t>
-  </si>
-  <si>
-    <t>NOC-AB14</t>
-  </si>
-  <si>
-    <t>NOC-AB16</t>
-  </si>
-  <si>
-    <t>NOC-AB17</t>
-  </si>
-  <si>
-    <t>NOC-AB18</t>
-  </si>
-  <si>
-    <t>NOC-AB19</t>
-  </si>
-  <si>
-    <t>NOC-AB20</t>
-  </si>
-  <si>
     <t>Payment done</t>
   </si>
   <si>
-    <t xml:space="preserve">form filled </t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>amit.7105565120@yopmail.com</t>
-  </si>
-  <si>
-    <t>NOC-AB21</t>
-  </si>
-  <si>
-    <t>neha.9470723094@yopmail.com</t>
-  </si>
-  <si>
-    <t>NOC-AB22</t>
+    <t>RockWoods School</t>
+  </si>
+  <si>
+    <t>Loudoun Public School</t>
+  </si>
+  <si>
+    <t>Powhatan International School ..</t>
+  </si>
+  <si>
+    <t>Silver Oak School</t>
+  </si>
+  <si>
+    <t>Lotus Bloom Public School</t>
+  </si>
+  <si>
+    <t>Royal Crest Academy</t>
+  </si>
+  <si>
+    <t>Blue Ridge High School</t>
+  </si>
+  <si>
+    <t>Harmony World School</t>
+  </si>
+  <si>
+    <t>Golden Horizon School</t>
+  </si>
+  <si>
+    <t>New Era Public Academy</t>
+  </si>
+  <si>
+    <t>Evergreen Scholars School</t>
+  </si>
+  <si>
+    <t>Crystal Springs School</t>
+  </si>
+  <si>
+    <t>Wisdom Valley Academy</t>
+  </si>
+  <si>
+    <t>Pinecrest Public School</t>
+  </si>
+  <si>
+    <t>Global Vision International School</t>
+  </si>
+  <si>
+    <t>Sycamore Public School</t>
+  </si>
+  <si>
+    <t>Mirman Public School</t>
+  </si>
+  <si>
+    <t>Sneha Rajput</t>
+  </si>
+  <si>
+    <t>USED TGPVIZ</t>
+  </si>
+  <si>
+    <t>Cambridge Heights School</t>
+  </si>
+  <si>
+    <t>Prestige World School</t>
+  </si>
+  <si>
+    <t>Horizon Valley Academy</t>
+  </si>
+  <si>
+    <t>Shining Stars Public School</t>
+  </si>
+  <si>
+    <t>Hilltop Scholars School</t>
+  </si>
+  <si>
+    <t>Future Minds International School</t>
+  </si>
+  <si>
+    <t>Elite Crest Academy</t>
+  </si>
+  <si>
+    <t>Morning Glory Public School</t>
+  </si>
+  <si>
+    <t>Unity International School</t>
+  </si>
+  <si>
+    <t>Beacon Light Academy</t>
+  </si>
+  <si>
+    <t>rahul.7500203190@yopmail.com</t>
+  </si>
+  <si>
+    <t>amitsen.7839377900@yopmail.com</t>
+  </si>
+  <si>
+    <t>neha.8800690994@yopmail.com</t>
+  </si>
+  <si>
+    <t>neha.7555210989@yopmail.com</t>
+  </si>
+  <si>
+    <t>priya.9004293242@yopmail.com</t>
+  </si>
+  <si>
+    <t>REVIEW DONE</t>
+  </si>
+  <si>
+    <t>karan.9425374392@yopmail.com</t>
+  </si>
+  <si>
+    <t>Karan Mahajan</t>
+  </si>
+  <si>
+    <t>riya.9020420036@yopmail.com</t>
+  </si>
+  <si>
+    <t>raj.8909203050@yopmail.com</t>
+  </si>
+  <si>
+    <t>sonali.8392039111@yopmail.com</t>
+  </si>
+  <si>
+    <t>sneha.8217914541@yopmail.com</t>
+  </si>
+  <si>
+    <t>Scholars Public Academy</t>
+  </si>
+  <si>
+    <t>Northstar Central School</t>
+  </si>
+  <si>
+    <t>Springfield Girls Academy</t>
+  </si>
+  <si>
+    <t>Emerald Green Girls School</t>
+  </si>
+  <si>
+    <t>HVWCDU</t>
+  </si>
+  <si>
+    <t>JSCP0Y</t>
+  </si>
+  <si>
+    <t>4ST1VC</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>0RXBHS</t>
+  </si>
+  <si>
+    <t>ALEGYJ</t>
+  </si>
+  <si>
+    <t>Scholar  Academy</t>
+  </si>
+  <si>
+    <t>Northstar Girls Academy</t>
+  </si>
+  <si>
+    <t>Springfield Girls School</t>
+  </si>
+  <si>
+    <t>Emerald Girls School</t>
+  </si>
+  <si>
+    <t>rahul.7766990113@yopmail.com</t>
+  </si>
+  <si>
+    <t>neha.8994421189@yopmail.com</t>
+  </si>
+  <si>
+    <t>amitsen.7142128300@yopmail.com</t>
+  </si>
+  <si>
+    <t>priya.9182736455@yopmail.com</t>
+  </si>
+  <si>
+    <t>neha.8833995577@yopmail.com</t>
+  </si>
+  <si>
+    <t>raj.9023204202@yopmail.com</t>
+  </si>
+  <si>
+    <t>riya.7861224324@yopmail.com</t>
+  </si>
+  <si>
+    <t>karan.9951015200@yopmail.com</t>
+  </si>
+  <si>
+    <t>sonali.8834923202@yopmail.com</t>
+  </si>
+  <si>
+    <t>sneha.9534825530@yopmail.com</t>
+  </si>
+  <si>
+    <t>NOC-AB54</t>
+  </si>
+  <si>
+    <t>NOC-AB55</t>
+  </si>
+  <si>
+    <t>NOC-AB56</t>
+  </si>
+  <si>
+    <t>NOC-AB57</t>
+  </si>
+  <si>
+    <t>NOC-AB58</t>
+  </si>
+  <si>
+    <t>NOC-AB59</t>
+  </si>
+  <si>
+    <t>NOC-AB60</t>
+  </si>
+  <si>
+    <t>NOC-AB61</t>
+  </si>
+  <si>
+    <t>NOC-AB62</t>
+  </si>
+  <si>
+    <t>NOC-AB63</t>
+  </si>
+  <si>
+    <t>ZQJWXW</t>
+  </si>
+  <si>
+    <t>4MQC3G</t>
+  </si>
+  <si>
+    <t>JVVC7I</t>
+  </si>
+  <si>
+    <t>JSWDHJ</t>
+  </si>
+  <si>
+    <t>2MK8WX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW DONE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">not done - issue occurred </t>
+  </si>
+  <si>
+    <t>Review Done</t>
   </si>
 </sst>
 </file>
@@ -951,7 +1119,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -969,6 +1137,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1284,10 +1456,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F188EA10-1DF6-4609-BA6F-007672B2DE7B}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1295,50 +1467,47 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1346,7 +1515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -1354,7 +1523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1362,17 +1531,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>3</v>
@@ -1386,15 +1555,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB661490-AEFF-419B-9D8E-B1B0487F0DAB}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.26953125" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29">
+    <row r="1" spans="1:4" ht="29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1408,7 +1576,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1416,16 +1584,13 @@
         <v>15</v>
       </c>
       <c r="C2" s="2">
-        <v>7102323017</v>
+        <v>7766990113</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1433,16 +1598,13 @@
         <v>15</v>
       </c>
       <c r="C3" s="2">
-        <v>8189090889</v>
+        <v>8994421189</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1450,16 +1612,13 @@
         <v>15</v>
       </c>
       <c r="C4">
-        <v>7105565120</v>
+        <v>7142128300</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1467,13 +1626,13 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>9940409940</v>
+        <v>9182736455</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1481,13 +1640,13 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>9470723094</v>
+        <v>8833995577</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1495,13 +1654,13 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>8930308930</v>
+        <v>9023204202</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -1509,13 +1668,13 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>9339337336</v>
+        <v>7861224324</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1523,53 +1682,62 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>9109883327</v>
+        <v>9951015200</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C10">
-        <v>8398291920</v>
+        <v>8834923202</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C11">
-        <v>9020405020</v>
+        <v>9534825530</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>246</v>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="C14">
+        <v>8398291920</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{07B2F22C-5D67-4BBB-940E-AA0EDC2682B2}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{54CD23EA-6FB4-4C49-B725-974AE210A5DD}"/>
-    <hyperlink ref="D5" r:id="rId3" xr:uid="{EDE87E61-5081-4B9A-82FD-CE622AC5EBA5}"/>
-    <hyperlink ref="D8" r:id="rId4" xr:uid="{30E3AD14-59D0-48D4-83A2-476857F4F8DA}"/>
-    <hyperlink ref="D9" r:id="rId5" xr:uid="{8DCF6F87-B1AE-4AC0-8C36-7231B5DF120A}"/>
-    <hyperlink ref="D3" r:id="rId6" xr:uid="{250730D2-4221-41EA-990B-5C7F23095CDD}"/>
-    <hyperlink ref="D7" r:id="rId7" xr:uid="{A9AA5CB8-C6B0-4F90-A3BA-7E259F62A2E3}"/>
-    <hyperlink ref="D6" r:id="rId8" xr:uid="{6189F085-F58D-46F0-9FBE-CF63C00BD26D}"/>
-    <hyperlink ref="D10" r:id="rId9" xr:uid="{89DBF00E-5D1A-4DB0-9556-439BB4BA9AD5}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{E94B873D-DAF4-436B-86D9-D89180C89387}"/>
+    <hyperlink ref="D14" r:id="rId1" xr:uid="{80AA749C-8199-4EAF-8D7F-43E56F8DD6D7}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{DB4E6256-2693-4F47-B9F7-17C918438AEC}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{42FD32D8-BE3B-4645-90A5-C21B10632239}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{6159EB68-6378-46AC-87BD-17A0C44D13AB}"/>
+    <hyperlink ref="D8" r:id="rId5" xr:uid="{B07D6E4A-B5A0-4A40-8FCC-A820381E5CA0}"/>
+    <hyperlink ref="D9" r:id="rId6" xr:uid="{F2E89491-2A56-4018-A513-989F2839CA22}"/>
+    <hyperlink ref="D3" r:id="rId7" xr:uid="{1983B00D-3AF9-486E-BC3A-B06C5DFBB1B5}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{B4232F40-B0ED-4DCE-8E93-3D2342182652}"/>
+    <hyperlink ref="D6" r:id="rId9" xr:uid="{B8524C11-C07A-4CD3-A7E6-DBC5F01C4D32}"/>
+    <hyperlink ref="D10" r:id="rId10" xr:uid="{BCFD86D3-C7BD-4DBE-8B7D-CBB7E596E70B}"/>
+    <hyperlink ref="D11" r:id="rId11" xr:uid="{4812F87D-F67A-492A-8701-B96DCC967B63}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1577,13 +1745,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9DA6ED1-12A9-4ACC-9AEC-06120A424A99}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="14.81640625" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="29">
+    <row r="1" spans="1:6" ht="29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1597,7 +1767,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6" ht="29">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1605,13 +1775,16 @@
         <v>15</v>
       </c>
       <c r="C2" s="2">
-        <v>7102323017</v>
+        <v>7766990113</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>330</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="43.5">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1619,11 +1792,16 @@
         <v>15</v>
       </c>
       <c r="C3" s="2">
-        <v>8189090889</v>
-      </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4">
+        <v>8994421189</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1631,10 +1809,16 @@
         <v>15</v>
       </c>
       <c r="C4">
-        <v>7105565120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>7142128300</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1642,10 +1826,16 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>9940409940</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>9182736455</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1653,10 +1843,13 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>9470723094</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>8833995577</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="29">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1664,10 +1857,16 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>8930308930</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>9023204202</v>
+      </c>
+      <c r="D7" t="s">
+        <v>300</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -1675,10 +1874,13 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>9339337336</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>7861224324</v>
+      </c>
+      <c r="D8" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="29">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1686,44 +1888,63 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>9109883327</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>9951015200</v>
+      </c>
+      <c r="D9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" ht="29">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C10">
-        <v>8398291920</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>8834923202</v>
+      </c>
+      <c r="D10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C11">
-        <v>9020405020</v>
-      </c>
+        <v>9534825530</v>
+      </c>
+      <c r="D11" t="s">
+        <v>305</v>
+      </c>
+      <c r="F11" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472E1A79-97FB-4866-BF3B-D45E6C89A57E}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11.453125" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" customWidth="1"/>
     <col min="5" max="5" width="13.26953125" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="36.26953125" customWidth="1"/>
@@ -1738,31 +1959,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="43.5">
@@ -1770,66 +1991,66 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2">
+        <v>7766990113</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I2" s="2">
+        <v>22776690113</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="2">
-        <v>7102323017</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="I2" s="2">
-        <v>97102323017</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="29">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="58">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="F3" s="2">
-        <v>8189090889</v>
+        <v>8994421189</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>240</v>
+        <v>311</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="I3" s="2">
-        <v>98189090889</v>
+        <v>18994421189</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="29">
@@ -1837,95 +2058,95 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4">
+        <v>7142128300</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I4">
+        <v>17142128300</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F4">
-        <v>7105565120</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="I4">
-        <v>71055651200</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="29">
+    </row>
+    <row r="5" spans="1:11" ht="43.5">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>9940409940</v>
+        <v>9182736455</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="I5">
-        <v>99404809940</v>
+        <v>99182736455</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="58">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="43.5">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>9470723094</v>
+        <v>8833995577</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="I6">
-        <v>89470723094</v>
+        <v>23833995577</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="29">
@@ -1933,31 +2154,31 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="F7">
-        <v>8930308930</v>
+        <v>9023204202</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>242</v>
+        <v>315</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="I7">
-        <v>98930308930</v>
+        <v>25323204202</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="29">
@@ -1965,127 +2186,514 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>254</v>
+        <v>306</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>9339337336</v>
+        <v>7861224324</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>243</v>
+        <v>316</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="I8">
-        <v>79339337336</v>
+        <v>53786124324</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="29">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="43.5">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="F9">
-        <v>9109883327</v>
+        <v>9951015200</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>244</v>
+        <v>317</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="I9">
-        <v>91109883327</v>
+        <v>33995115200</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="29">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F10">
-        <v>8398291920</v>
+        <v>8834923202</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>245</v>
+        <v>318</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="I10">
-        <v>89398291920</v>
+        <v>21883923202</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="29">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F11">
+        <v>9534825530</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I11">
+        <v>20034825530</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="3"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="3"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="3"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="3"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="43.5">
+      <c r="B17" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F11">
+      <c r="C17" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" ht="43.5">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="43.5">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G29">
+        <v>7190085120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="43.5">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G30" s="2">
+        <v>8189090889</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="43.5">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G31">
+        <v>7105565120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="58">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G32">
+        <v>9940409940</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="29">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G33">
+        <v>9470723094</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="43.5">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G34">
+        <v>8930308930</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="43.5">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G35">
+        <v>9339337336</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="29">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G36">
+        <v>9102289027</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="29">
+      <c r="F37" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G37">
+        <v>8398507920</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="F38" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G38">
         <v>9020405020</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="H11" s="3" t="s">
+    </row>
+    <row r="39" spans="1:7">
+      <c r="F39" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G39" s="2">
+        <v>7532353190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="29">
+      <c r="F40" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G40" s="2">
+        <v>8283219289</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="F41" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G41">
+        <v>7190285120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="29">
+      <c r="F42" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G42">
+        <v>9930117900</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="29">
+      <c r="F43" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G43">
+        <v>9400679904</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="F44" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G44">
+        <v>8923239930</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="29">
+      <c r="F45" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G45">
+        <v>9000020136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="29">
+      <c r="F46" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G46">
+        <v>9909022392</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="29">
+      <c r="F47" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G47">
+        <v>8020231013</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="29">
+      <c r="F48" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G48">
+        <v>9020231201</v>
+      </c>
+    </row>
+    <row r="49" spans="6:9" ht="29">
+      <c r="F49" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G49" s="2">
+        <v>7500203190</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="6:9" ht="29">
+      <c r="F50" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="I11">
-        <v>90020405020</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>36</v>
+      <c r="G50" s="2">
+        <v>7555210989</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="6:9" ht="29">
+      <c r="F51" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G51">
+        <v>7839377900</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="6:9" ht="29">
+      <c r="F52" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G52">
+        <v>9004293242</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="6:9" ht="29">
+      <c r="F53" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G53">
+        <v>8800690994</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="6:9" ht="29">
+      <c r="F54" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G54">
+        <v>8909203050</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="6:9" ht="29">
+      <c r="F55" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G55">
+        <v>9020420036</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" spans="6:9" ht="29">
+      <c r="F56" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G56">
+        <v>9425374392</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="57" spans="6:9" ht="29">
+      <c r="F57" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G57">
+        <v>8392039111</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="58" spans="6:9" ht="29">
+      <c r="F58" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G58">
+        <v>8217914541</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -2101,20 +2709,30 @@
     <hyperlink ref="H10:H11" r:id="rId8" display="www.royalinternational.edu.in" xr:uid="{0BEAFDF5-94E3-4AF2-B740-4DE8D04CE357}"/>
     <hyperlink ref="H10" r:id="rId9" xr:uid="{9BDBB02E-7FC3-4019-8CD9-552F0186FD91}"/>
     <hyperlink ref="H11" r:id="rId10" xr:uid="{EC9D3599-68A7-4B69-B43A-40A9EF22F481}"/>
-    <hyperlink ref="G2" r:id="rId11" xr:uid="{6052103B-4EFB-4EFF-9BE1-21734A28673F}"/>
-    <hyperlink ref="G4" r:id="rId12" xr:uid="{8F582ACE-2C87-4128-A53B-5A1755184698}"/>
-    <hyperlink ref="G5" r:id="rId13" xr:uid="{93F6C467-0AA6-45B2-99E9-A6C3E14AD539}"/>
-    <hyperlink ref="G8" r:id="rId14" xr:uid="{70D5E972-3624-47D1-941A-6A98C8629E43}"/>
-    <hyperlink ref="G9" r:id="rId15" xr:uid="{2C12716C-ED07-4E9E-BC27-865026D3D9E8}"/>
-    <hyperlink ref="G3" r:id="rId16" xr:uid="{FD085D23-4F44-4B01-966E-33B8BADF51CE}"/>
-    <hyperlink ref="G7" r:id="rId17" xr:uid="{560C6A9D-0219-4C71-8C33-1983E5D18EF7}"/>
-    <hyperlink ref="G6" r:id="rId18" xr:uid="{D9EC115C-83A7-4823-97D0-D545DCFC1BF0}"/>
-    <hyperlink ref="G10" r:id="rId19" xr:uid="{C78F4DA1-630F-40E3-8F87-7F9B09761530}"/>
-    <hyperlink ref="G11" r:id="rId20" xr:uid="{CEB75B73-6357-4B41-8E29-F8F5A0CB0F7D}"/>
-    <hyperlink ref="H9" r:id="rId21" display="www.greenfieldcountryday.com" xr:uid="{5C201A61-9E87-4E02-AFB6-DEF7F844F531}"/>
+    <hyperlink ref="H9" r:id="rId11" display="www.greenfieldcountryday.com" xr:uid="{5C201A61-9E87-4E02-AFB6-DEF7F844F531}"/>
+    <hyperlink ref="G2" r:id="rId12" xr:uid="{2336B88E-265B-43F3-A03D-927FC7D1CC47}"/>
+    <hyperlink ref="G4" r:id="rId13" xr:uid="{4EFAFE8B-437C-4232-A7CE-3B927AF88D3B}"/>
+    <hyperlink ref="G5" r:id="rId14" xr:uid="{BC0B0B35-F909-4A53-9820-DAB9257937DA}"/>
+    <hyperlink ref="G8" r:id="rId15" xr:uid="{74279D33-D6FF-4133-B81C-4DB058C2DD11}"/>
+    <hyperlink ref="G9" r:id="rId16" xr:uid="{787E8126-6C8D-4A6B-8F44-69391A6520FA}"/>
+    <hyperlink ref="G3" r:id="rId17" xr:uid="{E0B4E327-EA88-4F9D-BE30-763987FA8CD2}"/>
+    <hyperlink ref="G7" r:id="rId18" xr:uid="{B8B3E9D7-2C0C-4520-845F-B86856F1B352}"/>
+    <hyperlink ref="G6" r:id="rId19" xr:uid="{1D20B212-B322-4643-968B-AB7870DA3934}"/>
+    <hyperlink ref="G10" r:id="rId20" xr:uid="{69E541CB-CD11-41DD-8D07-C9D3F1A143F0}"/>
+    <hyperlink ref="G11" r:id="rId21" xr:uid="{0052F672-A868-4EC7-8722-8A0C9BE6FEAD}"/>
+    <hyperlink ref="H49" r:id="rId22" xr:uid="{0597F66F-2388-43F9-9D07-2A2C5A3C7B03}"/>
+    <hyperlink ref="H51" r:id="rId23" xr:uid="{447DD06C-F932-44E2-BD5D-CB2C335E52A6}"/>
+    <hyperlink ref="H52" r:id="rId24" xr:uid="{4D57A358-0798-4ACF-A07E-1822978337EF}"/>
+    <hyperlink ref="H55" r:id="rId25" xr:uid="{D3A1FF19-5800-4C97-8371-69044EA9FDDD}"/>
+    <hyperlink ref="H56" r:id="rId26" xr:uid="{F0F5692A-15B4-46C4-AE56-A1C5209BBC78}"/>
+    <hyperlink ref="H50" r:id="rId27" xr:uid="{49CF07E3-258B-4B1F-8C1F-EA2271A717F0}"/>
+    <hyperlink ref="H54" r:id="rId28" xr:uid="{C8BFA204-D457-4B2B-978C-2AE96457722E}"/>
+    <hyperlink ref="H53" r:id="rId29" xr:uid="{85DA1864-4BC1-482B-B712-FF124AF49DA8}"/>
+    <hyperlink ref="H57" r:id="rId30" xr:uid="{4FF5C26A-5549-49D2-9C4D-B51675D5D90A}"/>
+    <hyperlink ref="H58" r:id="rId31" xr:uid="{294D9993-B1D5-430D-8EFA-1D0FBA0259F0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId22"/>
+  <pageSetup orientation="portrait" r:id="rId32"/>
 </worksheet>
 </file>
 
@@ -2134,25 +2752,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="43.5">
@@ -2160,25 +2778,25 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G2" s="2">
         <v>313001</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="43.5">
@@ -2186,25 +2804,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G3" s="2">
         <v>313001</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="58">
@@ -2212,25 +2830,25 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G4" s="2">
         <v>313002</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="58">
@@ -2238,25 +2856,25 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G5" s="2">
         <v>313002</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="58">
@@ -2264,25 +2882,25 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G6" s="2">
         <v>313002</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="58">
@@ -2290,25 +2908,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G7" s="2">
         <v>313003</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5">
@@ -2316,25 +2934,25 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G8" s="2">
         <v>313003</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.5">
@@ -2342,77 +2960,77 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G9" s="2">
         <v>313003</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.5">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G10" s="2">
         <v>313003</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.5">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="G11" s="2">
         <v>313003</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2436,25 +3054,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="43.5">
@@ -2462,25 +3080,25 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="43.5">
@@ -2488,25 +3106,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="58">
@@ -2514,25 +3132,25 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5">
@@ -2540,25 +3158,25 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="58">
@@ -2566,25 +3184,25 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="58">
@@ -2592,25 +3210,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="72.5">
@@ -2618,25 +3236,25 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="58">
@@ -2644,77 +3262,77 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="58">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="58">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>274</v>
+        <v>329</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2731,7 +3349,7 @@
     <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.1796875" customWidth="1"/>
     <col min="6" max="6" width="16.1796875" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="29">
@@ -2739,19 +3357,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="43.5">
@@ -2759,230 +3377,210 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="F2" s="2">
-        <v>207102323017</v>
-      </c>
-      <c r="G2" s="2">
-        <v>7102323017</v>
-      </c>
+        <v>340766990117</v>
+      </c>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:7" ht="43.5">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="F3" s="2">
-        <v>208189090889</v>
-      </c>
-      <c r="G3" s="2">
-        <v>8189090889</v>
-      </c>
+        <v>899442118989</v>
+      </c>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" ht="43.5">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="F4" s="2">
-        <v>277105565650</v>
-      </c>
-      <c r="G4">
-        <v>7105565650</v>
-      </c>
+        <v>344212983000</v>
+      </c>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7" ht="43.5">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F5" s="2">
-        <v>299404099408</v>
-      </c>
-      <c r="G5">
-        <v>9940409940</v>
-      </c>
+        <v>927364559008</v>
+      </c>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" ht="43.5">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="F6" s="2">
-        <v>7001470723094</v>
-      </c>
-      <c r="G6">
-        <v>9423023094</v>
-      </c>
+        <v>7324833995577</v>
+      </c>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" ht="43.5">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="F7" s="2">
-        <v>208439309330</v>
-      </c>
-      <c r="G7">
-        <v>8930308930</v>
-      </c>
+        <v>902320420190</v>
+      </c>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7" ht="29">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="F8" s="2">
-        <v>293393373361</v>
-      </c>
-      <c r="G8">
-        <v>9339337336</v>
-      </c>
+        <v>9017861224324</v>
+      </c>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" ht="43.5">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="F9" s="2">
-        <v>910988332701</v>
-      </c>
-      <c r="G9">
-        <v>9109883327</v>
-      </c>
+        <v>9951010090001</v>
+      </c>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" ht="43.5">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F10" s="2">
-        <v>208398291920</v>
-      </c>
-      <c r="G10">
-        <v>8398291920</v>
-      </c>
+        <v>883492834401</v>
+      </c>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7" ht="43.5">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F11" s="2">
-        <v>290204050202</v>
-      </c>
-      <c r="G11">
-        <v>9020405020</v>
-      </c>
+        <v>9534825519021</v>
+      </c>
+      <c r="G11" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -3004,49 +3602,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="72.5">
@@ -3054,49 +3652,49 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="G2" s="2">
         <v>4800</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="72.5">
@@ -3104,49 +3702,49 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="G3" s="2">
         <v>5000</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="72.5">
@@ -3154,49 +3752,49 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G4" s="2">
         <v>5200</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="72.5">
@@ -3204,49 +3802,49 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="D5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G5" s="2">
         <v>4700</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="72.5">
@@ -3254,49 +3852,49 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="D6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="G6" s="2">
         <v>5500</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="72.5">
@@ -3304,49 +3902,49 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="G7" s="2">
         <v>5300</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="72.5">
@@ -3354,49 +3952,49 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G8" s="2">
         <v>4900</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="72.5">
@@ -3404,149 +4002,149 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="G9" s="2">
         <v>5100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="M9" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N9" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="O9" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="P9" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="72.5">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="G10" s="2">
         <v>5100</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="72.5">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="G11" s="2">
         <v>5100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="M11" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3576,25 +4174,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="72.5">
@@ -3602,25 +4200,25 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="72.5">
@@ -3628,25 +4226,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72.5">
@@ -3654,25 +4252,25 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="72.5">
@@ -3680,25 +4278,25 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="72.5">
@@ -3706,25 +4304,25 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="72.5">
@@ -3732,25 +4330,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="72.5">
@@ -3758,25 +4356,25 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="72.5">
@@ -3784,77 +4382,77 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="72.5">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="72.5">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
